--- a/data/EVALUACIONES/MOVILIDAD/Valores de referencia pruebas.xlsx
+++ b/data/EVALUACIONES/MOVILIDAD/Valores de referencia pruebas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30416"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\EVALUACIONES\MOVILIDAD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\EVALUACIONES\MOVILIDAD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9268BCB0-B898-439A-BFCD-57A97881AD89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{9268BCB0-B898-439A-BFCD-57A97881AD89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5778D89-E866-4160-BFE4-8112597EB5DA}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="20">
   <si>
     <t>DORSIFLEX_D</t>
   </si>
@@ -45,9 +45,6 @@
     <t>FLEX_CAD_I</t>
   </si>
   <si>
-    <t>LUMBAR</t>
-  </si>
-  <si>
     <t>Criterio_Verde</t>
   </si>
   <si>
@@ -82,21 +79,6 @@
   </si>
   <si>
     <t>grados</t>
-  </si>
-  <si>
-    <t>&gt;45</t>
-  </si>
-  <si>
-    <t>40−45</t>
-  </si>
-  <si>
-    <t>&lt;40</t>
-  </si>
-  <si>
-    <t>&gt;80</t>
-  </si>
-  <si>
-    <t>70−80</t>
   </si>
   <si>
     <t>&lt;70</t>
@@ -151,7 +133,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -162,19 +144,6 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </right>
       <top style="thin">
         <color theme="4" tint="0.39997558519241921"/>
       </top>
@@ -215,14 +184,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -230,54 +198,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="8">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color rgb="FFCCCCCC"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFCCCCCC"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -459,6 +379,54 @@
         </right>
       </border>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -473,14 +441,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{71D4C70F-3244-4FFC-B54B-D06E2ABC9403}" name="Tabla1" displayName="Tabla1" ref="A1:E8" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1" tableBorderDxfId="7">
-  <autoFilter ref="A1:E8" xr:uid="{71D4C70F-3244-4FFC-B54B-D06E2ABC9403}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{71D4C70F-3244-4FFC-B54B-D06E2ABC9403}" name="Tabla1" displayName="Tabla1" ref="A1:E7" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6" tableBorderDxfId="5">
+  <autoFilter ref="A1:E7" xr:uid="{71D4C70F-3244-4FFC-B54B-D06E2ABC9403}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{5A9668BE-80DA-4DD0-B567-BB7F9AA892CF}" name="Prueba" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{E4956627-85A8-4EE2-A009-3ADECCBCD266}" name="Criterio_Verde" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{24D98243-4C99-43FB-9A08-F58DCAFC5B0A}" name="Criterio_Amarillo" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{16582C5D-A047-4796-9F43-A3A550A13CAF}" name="Criterio_Rojo" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{254CB1D3-03CB-40D8-A33A-8231A103B8B6}" name="Unidad" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{5A9668BE-80DA-4DD0-B567-BB7F9AA892CF}" name="Prueba" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{E4956627-85A8-4EE2-A009-3ADECCBCD266}" name="Criterio_Verde" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{24D98243-4C99-43FB-9A08-F58DCAFC5B0A}" name="Criterio_Amarillo" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{16582C5D-A047-4796-9F43-A3A550A13CAF}" name="Criterio_Rojo" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{254CB1D3-03CB-40D8-A33A-8231A103B8B6}" name="Unidad" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -749,150 +717,133 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5546875" customWidth="1"/>
-    <col min="3" max="3" width="17.44140625" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+    <col min="1" max="1" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.54296875" customWidth="1"/>
+    <col min="3" max="3" width="17.453125" customWidth="1"/>
+    <col min="4" max="4" width="14.453125" customWidth="1"/>
     <col min="5" max="5" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>10</v>
-      </c>
     </row>
-    <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>14</v>
-      </c>
     </row>
-    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>14</v>
-      </c>
     </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>18</v>
-      </c>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>18</v>
-      </c>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="4" t="s">
+      <c r="B6" s="2">
+        <v>80</v>
+      </c>
+      <c r="C6" s="2">
+        <v>75</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="E6" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="4" t="s">
+      <c r="B7" s="2">
+        <v>80</v>
+      </c>
+      <c r="C7" s="2">
+        <v>75</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>18</v>
+      <c r="E7" s="3" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
